--- a/reports/一级子公司B_利润表_2025-03.xlsx
+++ b/reports/一级子公司B_利润表_2025-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>48070958</v>
+        <v>63865132</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14199312</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>39098320</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>200863</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>554552</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>180400</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>498928</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>149961</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>415320</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>139623</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>386994</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>79627</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>220714</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>59652</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>165228</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>48070958</v>
+        <v>63055006</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13389186</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>7974394</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>21980004</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1198995</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>3299591</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>601004</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>1652182</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4015557</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>11034938</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>402168</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>1105622</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>301800</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>830599</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>502760</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>1385871</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>401629</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>1109104</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>47990784</v>
+        <v>48091478</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>132474529</v>
+        <v>133033479</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>80174</v>
+        <v>79952</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>240167</v>
+        <v>240758</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>897307</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>2487201</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>597083</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1654931</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>44400564</v>
+        <v>56889732</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>25250773</v>
+        <v>32092638</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>149205</v>
+        <v>7165395</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>413200</v>
+        <v>19781322</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>25101568</v>
+        <v>24927243</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>69102973</v>
+        <v>68691637</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1499247</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>4125143</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>480957</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1322048</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>301242</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>827835</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>362001</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>995303</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>271619</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>747677</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>180968</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>498961</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>150573</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>415910</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1193338</v>
+        <v>1201899</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3305304</v>
+        <v>3325446</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>40179</v>
+        <v>39963</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>110581</v>
+        <v>110709</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2492732</v>
+        <v>2491801</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6892563</v>
+        <v>6907157</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>15015035</v>
+        <v>14924223</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>41416184</v>
+        <v>41362646</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2485162</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>6881486</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>448686</v>
+        <v>447402</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1348722</v>
+        <v>1344721</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401797</v>
+        <v>398161</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1201773</v>
+        <v>1194482</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>29833</v>
+        <v>29922</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>89834</v>
+        <v>89598</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>134978</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>403556</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>263106</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>723166</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>90394</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>269963</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67883</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>202861</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>113172</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>338643</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>376958</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1039586</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>60213</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>180834</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>45056</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>135546</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>74905</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>225620</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52313</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>157654</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37304</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>112391</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>29821</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>89753</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22372</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>67227</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3670394</v>
+        <v>7090498</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-109210</v>
+        <v>4511563</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>150026</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>412660</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37598</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>112298</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>59700</v>
+        <v>60276</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>179703</v>
+        <v>180023</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3610694</v>
+        <v>7180248</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1789243</v>
+        <v>1810681</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>5389232</v>
+        <v>5419230</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1821451</v>
+        <v>5369567</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1821451</v>
+        <v>5369567</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1821451</v>
+        <v>5369567</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1821451</v>
+        <v>5369567</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1821451</v>
+        <v>5369567</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
